--- a/data/output/feature_ablation.xlsx
+++ b/data/output/feature_ablation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,20 +486,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>contributing_features</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>features_considered</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
@@ -542,15 +557,24 @@
         <v>0.709</v>
       </c>
       <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O2" t="n">
         <v>886</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>2679</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>595</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>382</v>
       </c>
     </row>
@@ -591,15 +615,24 @@
         <v>0.701</v>
       </c>
       <c r="L3" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="M3" t="n">
+        <v>38</v>
+      </c>
+      <c r="N3" t="n">
+        <v>56</v>
+      </c>
+      <c r="O3" t="n">
         <v>840</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>2751</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>523</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>428</v>
       </c>
     </row>
@@ -640,15 +673,24 @@
         <v>0.723</v>
       </c>
       <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" t="n">
         <v>880</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>2757</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>517</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>388</v>
       </c>
     </row>
@@ -689,15 +731,24 @@
         <v>0.735</v>
       </c>
       <c r="L5" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="M5" t="n">
+        <v>198</v>
+      </c>
+      <c r="N5" t="n">
+        <v>240</v>
+      </c>
+      <c r="O5" t="n">
         <v>811</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>2853</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>421</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>457</v>
       </c>
     </row>
